--- a/research/traditional_assets/database/data/colombia/colombia_drugs_pharmaceutical.xlsx
+++ b/research/traditional_assets/database/data/colombia/colombia_drugs_pharmaceutical.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-17.72151898734177</v>
+        <v>-8.240384615384615</v>
       </c>
       <c r="H2">
-        <v>-17.72151898734177</v>
+        <v>-8.240384615384615</v>
       </c>
       <c r="I2">
-        <v>-10.18987341772152</v>
+        <v>-14.42307692307692</v>
       </c>
       <c r="J2">
-        <v>-10.18987341772152</v>
+        <v>-14.42307692307692</v>
       </c>
       <c r="K2">
-        <v>-2.13</v>
+        <v>-3.89</v>
       </c>
       <c r="L2">
-        <v>-13.48101265822785</v>
+        <v>-37.40384615384615</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.44</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="V2">
-        <v>0.1589403973509934</v>
+        <v>0.02693498452012384</v>
       </c>
       <c r="W2">
-        <v>-0.5351758793969849</v>
+        <v>-0.9823232323232324</v>
       </c>
       <c r="X2">
-        <v>0.08046935739033592</v>
+        <v>0.1484554960436361</v>
       </c>
       <c r="Y2">
-        <v>-0.6156452367873207</v>
+        <v>-1.130778728366868</v>
       </c>
       <c r="Z2">
-        <v>0.03475582930048395</v>
+        <v>0.02810810810810811</v>
       </c>
       <c r="AA2">
-        <v>-0.3541575010998681</v>
+        <v>-0.4054054054054054</v>
       </c>
       <c r="AB2">
-        <v>0.07495005522807144</v>
+        <v>0.1314010537668055</v>
       </c>
       <c r="AC2">
-        <v>-0.4291075563279395</v>
+        <v>-0.5368064591722109</v>
       </c>
       <c r="AD2">
-        <v>1.18</v>
+        <v>0.969</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.18</v>
+        <v>0.969</v>
       </c>
       <c r="AG2">
-        <v>-0.26</v>
+        <v>0.882</v>
       </c>
       <c r="AH2">
-        <v>0.115234375</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="AI2">
-        <v>0.2295719844357977</v>
+        <v>0.9797775530839231</v>
       </c>
       <c r="AJ2">
-        <v>-0.02954545454545454</v>
+        <v>0.2144941634241245</v>
       </c>
       <c r="AK2">
-        <v>-0.07027027027027027</v>
+        <v>0.9778270509977827</v>
       </c>
       <c r="AL2">
-        <v>0.214</v>
+        <v>0.228</v>
       </c>
       <c r="AM2">
-        <v>0.214</v>
+        <v>0.228</v>
       </c>
       <c r="AN2">
-        <v>-1.008547008547009</v>
+        <v>-0.7396946564885496</v>
       </c>
       <c r="AO2">
-        <v>-7.523364485981309</v>
+        <v>-6.578947368421052</v>
       </c>
       <c r="AP2">
-        <v>0.2222222222222222</v>
+        <v>-0.6732824427480916</v>
       </c>
       <c r="AQ2">
-        <v>-7.523364485981309</v>
+        <v>-6.578947368421052</v>
       </c>
     </row>
     <row r="3">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-17.72151898734177</v>
+        <v>-8.240384615384615</v>
       </c>
       <c r="H3">
-        <v>-17.72151898734177</v>
+        <v>-8.240384615384615</v>
       </c>
       <c r="I3">
-        <v>-10.18987341772152</v>
+        <v>-14.42307692307692</v>
       </c>
       <c r="J3">
-        <v>-10.18987341772152</v>
+        <v>-14.42307692307692</v>
       </c>
       <c r="K3">
-        <v>-2.13</v>
+        <v>-3.89</v>
       </c>
       <c r="L3">
-        <v>-13.48101265822785</v>
+        <v>-37.40384615384615</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.44</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="V3">
-        <v>0.1589403973509934</v>
+        <v>0.02693498452012384</v>
       </c>
       <c r="W3">
-        <v>-0.5351758793969849</v>
+        <v>-0.9823232323232324</v>
       </c>
       <c r="X3">
-        <v>0.08046935739033592</v>
+        <v>0.1484554960436361</v>
       </c>
       <c r="Y3">
-        <v>-0.6156452367873207</v>
+        <v>-1.130778728366868</v>
       </c>
       <c r="Z3">
-        <v>0.03475582930048395</v>
+        <v>0.02810810810810811</v>
       </c>
       <c r="AA3">
-        <v>-0.3541575010998681</v>
+        <v>-0.4054054054054054</v>
       </c>
       <c r="AB3">
-        <v>0.07495005522807144</v>
+        <v>0.1314010537668055</v>
       </c>
       <c r="AC3">
-        <v>-0.4291075563279395</v>
+        <v>-0.5368064591722109</v>
       </c>
       <c r="AD3">
-        <v>1.18</v>
+        <v>0.969</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.18</v>
+        <v>0.969</v>
       </c>
       <c r="AG3">
-        <v>-0.26</v>
+        <v>0.882</v>
       </c>
       <c r="AH3">
-        <v>0.115234375</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="AI3">
-        <v>0.2295719844357977</v>
+        <v>0.9797775530839231</v>
       </c>
       <c r="AJ3">
-        <v>-0.02954545454545454</v>
+        <v>0.2144941634241245</v>
       </c>
       <c r="AK3">
-        <v>-0.07027027027027027</v>
+        <v>0.9778270509977827</v>
       </c>
       <c r="AL3">
-        <v>0.214</v>
+        <v>0.228</v>
       </c>
       <c r="AM3">
-        <v>0.214</v>
+        <v>0.228</v>
       </c>
       <c r="AN3">
-        <v>-1.008547008547009</v>
+        <v>-0.7396946564885496</v>
       </c>
       <c r="AO3">
-        <v>-7.523364485981309</v>
+        <v>-6.578947368421052</v>
       </c>
       <c r="AP3">
-        <v>0.2222222222222222</v>
+        <v>-0.6732824427480916</v>
       </c>
       <c r="AQ3">
-        <v>-7.523364485981309</v>
+        <v>-6.578947368421052</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/colombia/colombia_drugs_pharmaceutical.xlsx
+++ b/research/traditional_assets/database/data/colombia/colombia_drugs_pharmaceutical.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-8.240384615384615</v>
+        <v>-1.289784946236559</v>
       </c>
       <c r="H2">
-        <v>-8.240384615384615</v>
+        <v>-1.370967741935484</v>
       </c>
       <c r="I2">
-        <v>-14.42307692307692</v>
+        <v>-1.204094254843844</v>
       </c>
       <c r="J2">
-        <v>-14.42307692307692</v>
+        <v>-1.204094254843844</v>
       </c>
       <c r="K2">
-        <v>-3.89</v>
+        <v>-41.6</v>
       </c>
       <c r="L2">
-        <v>-37.40384615384615</v>
+        <v>-2.236559139784946</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.08699999999999999</v>
+        <v>6.47</v>
       </c>
       <c r="V2">
-        <v>0.02693498452012384</v>
+        <v>1.76775956284153</v>
       </c>
       <c r="W2">
-        <v>-0.9823232323232324</v>
+        <v>-0.5985611510791368</v>
       </c>
       <c r="X2">
-        <v>0.1484554960436361</v>
+        <v>0.142594246648171</v>
       </c>
       <c r="Y2">
-        <v>-1.130778728366868</v>
+        <v>-0.7411553977273078</v>
       </c>
       <c r="Z2">
-        <v>0.02810810810810811</v>
+        <v>0.3310741633384664</v>
       </c>
       <c r="AA2">
-        <v>-0.4054054054054054</v>
+        <v>-0.3986444980030798</v>
       </c>
       <c r="AB2">
-        <v>0.1314010537668055</v>
+        <v>0.1194864680710052</v>
       </c>
       <c r="AC2">
-        <v>-0.5368064591722109</v>
+        <v>-0.5181309660740849</v>
       </c>
       <c r="AD2">
-        <v>0.969</v>
+        <v>1.34</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.980765700477505</v>
       </c>
       <c r="AF2">
-        <v>0.969</v>
+        <v>3.320765700477506</v>
       </c>
       <c r="AG2">
-        <v>0.882</v>
+        <v>-3.149234299522494</v>
       </c>
       <c r="AH2">
-        <v>0.2307692307692308</v>
+        <v>0.4757022141926859</v>
       </c>
       <c r="AI2">
-        <v>0.9797775530839231</v>
+        <v>0.1005659811343952</v>
       </c>
       <c r="AJ2">
-        <v>0.2144941634241245</v>
+        <v>-6.165712177967961</v>
       </c>
       <c r="AK2">
-        <v>0.9778270509977827</v>
+        <v>-0.1186118070962397</v>
       </c>
       <c r="AL2">
-        <v>0.228</v>
+        <v>0.029</v>
       </c>
       <c r="AM2">
-        <v>0.228</v>
+        <v>0.029</v>
       </c>
       <c r="AN2">
-        <v>-0.7396946564885496</v>
+        <v>-0.06943005181347151</v>
       </c>
       <c r="AO2">
-        <v>-6.578947368421052</v>
+        <v>-799.9999999999999</v>
       </c>
       <c r="AP2">
-        <v>-0.6732824427480916</v>
+        <v>0.1631727616332898</v>
       </c>
       <c r="AQ2">
-        <v>-6.578947368421052</v>
+        <v>-799.9999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Blueberries Medical Corp. (CNSX:BBM)</t>
+          <t>Clever Leaves Holdings Inc. (NasdaqCM:CLVR)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-8.240384615384615</v>
+        <v>-1.289784946236559</v>
       </c>
       <c r="H3">
-        <v>-8.240384615384615</v>
+        <v>-1.370967741935484</v>
       </c>
       <c r="I3">
-        <v>-14.42307692307692</v>
+        <v>-1.204094254843844</v>
       </c>
       <c r="J3">
-        <v>-14.42307692307692</v>
+        <v>-1.204094254843844</v>
       </c>
       <c r="K3">
-        <v>-3.89</v>
+        <v>-41.6</v>
       </c>
       <c r="L3">
-        <v>-37.40384615384615</v>
+        <v>-2.236559139784946</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.08699999999999999</v>
+        <v>6.47</v>
       </c>
       <c r="V3">
-        <v>0.02693498452012384</v>
+        <v>1.76775956284153</v>
       </c>
       <c r="W3">
-        <v>-0.9823232323232324</v>
+        <v>-0.5985611510791368</v>
       </c>
       <c r="X3">
-        <v>0.1484554960436361</v>
+        <v>0.142594246648171</v>
       </c>
       <c r="Y3">
-        <v>-1.130778728366868</v>
+        <v>-0.7411553977273078</v>
       </c>
       <c r="Z3">
-        <v>0.02810810810810811</v>
+        <v>0.3310741633384664</v>
       </c>
       <c r="AA3">
-        <v>-0.4054054054054054</v>
+        <v>-0.3986444980030798</v>
       </c>
       <c r="AB3">
-        <v>0.1314010537668055</v>
+        <v>0.1194864680710052</v>
       </c>
       <c r="AC3">
-        <v>-0.5368064591722109</v>
+        <v>-0.5181309660740849</v>
       </c>
       <c r="AD3">
-        <v>0.969</v>
+        <v>1.34</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.980765700477505</v>
       </c>
       <c r="AF3">
-        <v>0.969</v>
+        <v>3.320765700477506</v>
       </c>
       <c r="AG3">
-        <v>0.882</v>
+        <v>-3.149234299522494</v>
       </c>
       <c r="AH3">
-        <v>0.2307692307692308</v>
+        <v>0.4757022141926859</v>
       </c>
       <c r="AI3">
-        <v>0.9797775530839231</v>
+        <v>0.1005659811343952</v>
       </c>
       <c r="AJ3">
-        <v>0.2144941634241245</v>
+        <v>-6.165712177967961</v>
       </c>
       <c r="AK3">
-        <v>0.9778270509977827</v>
+        <v>-0.1186118070962397</v>
       </c>
       <c r="AL3">
-        <v>0.228</v>
+        <v>0.029</v>
       </c>
       <c r="AM3">
-        <v>0.228</v>
+        <v>0.029</v>
       </c>
       <c r="AN3">
-        <v>-0.7396946564885496</v>
+        <v>-0.06943005181347151</v>
       </c>
       <c r="AO3">
-        <v>-6.578947368421052</v>
+        <v>-799.9999999999999</v>
       </c>
       <c r="AP3">
-        <v>-0.6732824427480916</v>
+        <v>0.1631727616332898</v>
       </c>
       <c r="AQ3">
-        <v>-6.578947368421052</v>
+        <v>-799.9999999999999</v>
       </c>
     </row>
   </sheetData>
